--- a/Plot/exposures_meta_analysis_breast_dietary.xlsx
+++ b/Plot/exposures_meta_analysis_breast_dietary.xlsx
@@ -537,12 +537,12 @@
       <c r="E2" s="4" t="n">
         <v>0.42</v>
       </c>
-      <c r="F2" s="4" t="inlineStr"/>
-      <c r="G2" s="4" t="inlineStr"/>
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="4" t="n"/>
       <c r="H2" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="6" t="inlineStr"/>
+      <c r="I2" s="6" t="n"/>
       <c r="J2" s="3" t="n">
         <v>305</v>
       </c>
@@ -568,12 +568,12 @@
       <c r="E3" s="4" t="n">
         <v>0.68</v>
       </c>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="inlineStr"/>
+      <c r="F3" s="4" t="n"/>
+      <c r="G3" s="4" t="n"/>
       <c r="H3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="6" t="inlineStr"/>
+      <c r="I3" s="6" t="n"/>
       <c r="J3" s="3" t="n">
         <v>415</v>
       </c>
@@ -673,12 +673,12 @@
       <c r="E6" s="4" t="n">
         <v>1.03</v>
       </c>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="4" t="n"/>
       <c r="H6" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="n"/>
       <c r="J6" s="3" t="n">
         <v>663</v>
       </c>
@@ -714,7 +714,7 @@
         <v>88.5</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.09173584726167613</v>
+        <v>0.09173584726167605</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>90844</v>
@@ -741,12 +741,12 @@
       <c r="E8" s="4" t="n">
         <v>1.03</v>
       </c>
-      <c r="F8" s="4" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="n"/>
+      <c r="G8" s="4" t="n"/>
       <c r="H8" s="5" t="n">
         <v>74.7</v>
       </c>
-      <c r="I8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="n"/>
       <c r="J8" s="3" t="n">
         <v>1370</v>
       </c>
@@ -772,12 +772,12 @@
       <c r="E9" s="4" t="n">
         <v>0.84</v>
       </c>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="n"/>
+      <c r="G9" s="4" t="n"/>
       <c r="H9" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="n"/>
       <c r="J9" s="3" t="n">
         <v>876</v>
       </c>
@@ -788,100 +788,100 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>legumes</t>
+          <t>black_cohosh</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>0.61</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.5</v>
+        <v>0.34</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>1.37</v>
-      </c>
+        <v>1.07</v>
+      </c>
+      <c r="F10" s="4" t="n"/>
+      <c r="G10" s="4" t="n"/>
       <c r="H10" s="5" t="n">
-        <v>94.09999999999999</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>0.001758518003460141</v>
-      </c>
+        <v>76.40000000000001</v>
+      </c>
+      <c r="I10" s="6" t="n"/>
       <c r="J10" s="3" t="n">
-        <v>273560</v>
+        <v>12594</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>15479</v>
+        <v>4413</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>black_cohosh</t>
+          <t>grape</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.34</v>
+        <v>0.38</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="F11" s="4" t="inlineStr"/>
-      <c r="G11" s="4" t="inlineStr"/>
+        <v>0.96</v>
+      </c>
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
       <c r="H11" s="5" t="n">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="I11" s="6" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="I11" s="6" t="n"/>
       <c r="J11" s="3" t="n">
-        <v>12594</v>
+        <v>1067</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>4413</v>
+        <v>359</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>grape</t>
+          <t>vitamin_b12</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="F12" s="4" t="inlineStr"/>
-      <c r="G12" s="4" t="inlineStr"/>
+        <v>0.95</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>2.42</v>
+      </c>
       <c r="H12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="6" t="inlineStr"/>
+        <v>88.7</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.09471360956321104</v>
+      </c>
       <c r="J12" s="3" t="n">
-        <v>1067</v>
+        <v>38506</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>359</v>
+        <v>8006</v>
       </c>
     </row>
     <row r="13">
@@ -912,7 +912,7 @@
         <v>54.6</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.2487315066792916</v>
+        <v>0.2487315066792918</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>43927</v>
@@ -924,174 +924,174 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>vitamin_b12</t>
+          <t>lutein</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.44</v>
+        <v>0.55</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.17</v>
+        <v>0.37</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2.42</v>
+        <v>1.2</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>88.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.09471360956321104</v>
+        <v>0.001205141873155634</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>38506</v>
+        <v>1061834</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>8006</v>
+        <v>45572</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>lutein</t>
+          <t>omega-3_fatty_acids</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>0.8</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.37</v>
+        <v>0.39</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>76.09999999999999</v>
+        <v>64.5</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.001205141873155637</v>
+        <v>0.4864450605937343</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>1061834</v>
+        <v>238479</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>45572</v>
+        <v>7644</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>omega-3_fatty_acids</t>
+          <t>antioxidants</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.39</v>
+        <v>0.33</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.16</v>
+        <v>1.49</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>64.5</v>
+        <v>86</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.4864450605937342</v>
+        <v>0.01777472721809745</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>238479</v>
+        <v>392499</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>7644</v>
+        <v>18643</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>oats</t>
+          <t>n-acetylcysteine</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>0.7</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.3</v>
+        <v>0.68</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="F17" s="4" t="inlineStr"/>
-      <c r="G17" s="4" t="inlineStr"/>
+        <v>0.73</v>
+      </c>
+      <c r="F17" s="4" t="n"/>
+      <c r="G17" s="4" t="n"/>
       <c r="H17" s="5" t="n">
-        <v>82.3</v>
-      </c>
-      <c r="I17" s="6" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="I17" s="6" t="n"/>
       <c r="J17" s="3" t="n">
-        <v>28604</v>
+        <v>91546</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>1075</v>
+        <v>11901</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>n-acetylcysteine</t>
+          <t>oats</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>0.7</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.68</v>
+        <v>0.3</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="F18" s="4" t="inlineStr"/>
-      <c r="G18" s="4" t="inlineStr"/>
+        <v>1.65</v>
+      </c>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
       <c r="H18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="6" t="inlineStr"/>
+        <v>82.3</v>
+      </c>
+      <c r="I18" s="6" t="n"/>
       <c r="J18" s="3" t="n">
-        <v>91546</v>
+        <v>28604</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>11901</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="19">
@@ -1134,75 +1134,69 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>mediterranean_diet</t>
+          <t>folic_acid</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="E20" s="4" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.51</v>
+        <v>0.43</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.07</v>
+        <v>1.21</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>87</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>2.930546567262829e-05</v>
+        <v>5.667201636158433e-06</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>540284</v>
+        <v>990467</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>28689</v>
+        <v>46628</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>fish_oil</t>
+          <t>mineral_supplements</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.49</v>
+        <v>0.43</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>4.78</v>
-      </c>
+        <v>1.17</v>
+      </c>
+      <c r="F21" s="4" t="n"/>
+      <c r="G21" s="4" t="n"/>
       <c r="H21" s="5" t="n">
-        <v>87.40000000000001</v>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>0.05582483881549634</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I21" s="6" t="n"/>
       <c r="J21" s="3" t="n">
-        <v>508253</v>
+        <v>836</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>62658</v>
+        <v>312</v>
       </c>
     </row>
     <row r="22">
@@ -1245,242 +1239,260 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>antioxidants</t>
+          <t>fish_oil</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.6</v>
+        <v>0.49</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.95</v>
+        <v>1.11</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.35</v>
+        <v>0.11</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.63</v>
+        <v>4.78</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>86.09999999999999</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.1077633081102808</v>
+        <v>0.05582483881549636</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>393342</v>
+        <v>508253</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>19057</v>
+        <v>62658</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>soy</t>
+          <t>legumes</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.32</v>
+        <v>0.45</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.76</v>
+        <v>1.22</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>91.09999999999999</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.03117076126282999</v>
+        <v>4.315818448979679e-05</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>919838</v>
+        <v>273560</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>32658</v>
+        <v>15479</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>vitamin_b1</t>
+          <t>soy</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>0.75</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="F25" s="4" t="inlineStr"/>
-      <c r="G25" s="4" t="inlineStr"/>
+        <v>0.87</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>1.76</v>
+      </c>
       <c r="H25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="6" t="inlineStr"/>
+        <v>91.09999999999999</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>0.03117076126282999</v>
+      </c>
       <c r="J25" s="3" t="n">
-        <v>38639</v>
+        <v>919838</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>853</v>
+        <v>32658</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>folic_acid</t>
+          <t>vitamin_b1</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.67</v>
+        <v>0.61</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="F26" s="4" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="G26" s="4" t="n">
-        <v>1.36</v>
-      </c>
+        <v>0.93</v>
+      </c>
+      <c r="F26" s="4" t="n"/>
+      <c r="G26" s="4" t="n"/>
       <c r="H26" s="5" t="n">
-        <v>85.5</v>
-      </c>
-      <c r="I26" s="6" t="n">
-        <v>0.002326013428354483</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I26" s="6" t="n"/>
       <c r="J26" s="3" t="n">
-        <v>990582</v>
+        <v>38639</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>46686</v>
+        <v>853</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>leucine</t>
+          <t>vitamin_e</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="D27" s="4" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="F27" s="4" t="n">
         <v>0.4</v>
       </c>
-      <c r="E27" s="4" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="F27" s="4" t="inlineStr"/>
-      <c r="G27" s="4" t="inlineStr"/>
+      <c r="G27" s="4" t="n">
+        <v>1.4</v>
+      </c>
       <c r="H27" s="5" t="n">
-        <v>92.8</v>
-      </c>
-      <c r="I27" s="6" t="inlineStr"/>
+        <v>77.7</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>0.004128823967049899</v>
+      </c>
       <c r="J27" s="3" t="n">
-        <v>197211</v>
+        <v>303677</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>10396</v>
+        <v>30794</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>bcaas</t>
+          <t>beta-carotene</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.4</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="F28" s="4" t="inlineStr"/>
-      <c r="G28" s="4" t="inlineStr"/>
+        <v>0.85</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>1.18</v>
+      </c>
       <c r="H28" s="5" t="n">
-        <v>92.8</v>
-      </c>
-      <c r="I28" s="6" t="inlineStr"/>
+        <v>82.59999999999999</v>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>0.01807598378940583</v>
+      </c>
       <c r="J28" s="3" t="n">
-        <v>197211</v>
+        <v>1684061</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>10396</v>
+        <v>114896</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>mineral_supplements</t>
+          <t>mediterranean_diet</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F29" s="4" t="inlineStr"/>
-      <c r="G29" s="4" t="inlineStr"/>
+        <v>0.83</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>1.08</v>
+      </c>
       <c r="H29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="6" t="inlineStr"/>
+        <v>87.2</v>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>4.147592651637327e-05</v>
+      </c>
       <c r="J29" s="3" t="n">
-        <v>7408</v>
+        <v>639823</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>3413</v>
+        <v>40922</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>isoleucine</t>
+          <t>bcaas</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
@@ -1495,12 +1507,12 @@
       <c r="E30" s="4" t="n">
         <v>1.48</v>
       </c>
-      <c r="F30" s="4" t="inlineStr"/>
-      <c r="G30" s="4" t="inlineStr"/>
+      <c r="F30" s="4" t="n"/>
+      <c r="G30" s="4" t="n"/>
       <c r="H30" s="5" t="n">
         <v>92.8</v>
       </c>
-      <c r="I30" s="6" t="inlineStr"/>
+      <c r="I30" s="6" t="n"/>
       <c r="J30" s="3" t="n">
         <v>197211</v>
       </c>
@@ -1511,211 +1523,199 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>cod_liver_oil</t>
+          <t>isoleucine</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
         <v>2</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.68</v>
+        <v>0.4</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F31" s="4" t="inlineStr"/>
-      <c r="G31" s="4" t="inlineStr"/>
+        <v>1.48</v>
+      </c>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="n"/>
       <c r="H31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="6" t="inlineStr"/>
+        <v>92.8</v>
+      </c>
+      <c r="I31" s="6" t="n"/>
       <c r="J31" s="3" t="n">
-        <v>4001</v>
+        <v>197211</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>1731</v>
+        <v>10396</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>beta-carotene</t>
+          <t>leucine</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F32" s="4" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="G32" s="4" t="n">
-        <v>1.4</v>
-      </c>
+        <v>1.48</v>
+      </c>
+      <c r="F32" s="4" t="n"/>
+      <c r="G32" s="4" t="n"/>
       <c r="H32" s="5" t="n">
-        <v>89.59999999999999</v>
-      </c>
-      <c r="I32" s="6" t="n">
-        <v>0.1405222253858072</v>
-      </c>
+        <v>92.8</v>
+      </c>
+      <c r="I32" s="6" t="n"/>
       <c r="J32" s="3" t="n">
-        <v>1684061</v>
+        <v>197211</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>114896</v>
+        <v>10396</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>betaine</t>
+          <t>cod_liver_oil</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
         <v>2</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.5</v>
+        <v>0.68</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="F33" s="4" t="inlineStr"/>
-      <c r="G33" s="4" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="4" t="n"/>
       <c r="H33" s="5" t="n">
-        <v>88.40000000000001</v>
-      </c>
-      <c r="I33" s="6" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="I33" s="6" t="n"/>
       <c r="J33" s="3" t="n">
-        <v>76198</v>
+        <v>4001</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>4797</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>miso</t>
+          <t>betaine</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="F34" s="4" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G34" s="4" t="n">
-        <v>33.61</v>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="F34" s="4" t="n"/>
+      <c r="G34" s="4" t="n"/>
       <c r="H34" s="5" t="n">
-        <v>57</v>
-      </c>
-      <c r="I34" s="6" t="n">
-        <v>0.5607534123225345</v>
-      </c>
+        <v>88.40000000000001</v>
+      </c>
+      <c r="I34" s="6" t="n"/>
       <c r="J34" s="3" t="n">
-        <v>87065</v>
+        <v>76198</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>751</v>
+        <v>4797</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>olive</t>
+          <t>miso</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>0.8</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.92</v>
+        <v>1.13</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.51</v>
+        <v>0.02</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>1.24</v>
+        <v>33.61</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>0.01389915282783273</v>
+        <v>0.5607534123225346</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>248595</v>
+        <v>87065</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>16870</v>
+        <v>751</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>yogurt</t>
+          <t>olive</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.57</v>
+        <v>0.51</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>58.7</v>
+        <v>81</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>0.0321383112172301</v>
+        <v>0.01389915282783274</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>20962</v>
+        <v>248595</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>40377</v>
+        <v>16870</v>
       </c>
     </row>
     <row r="37">
@@ -1746,7 +1746,7 @@
         <v>90.8</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>0.5897124894853762</v>
+        <v>0.5897124894853758</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>190614</v>
@@ -1758,38 +1758,44 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>flax</t>
+          <t>yogurt</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C38" s="4" t="n">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="F38" s="4" t="inlineStr"/>
-      <c r="G38" s="4" t="inlineStr"/>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>1.2</v>
+      </c>
       <c r="H38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="6" t="inlineStr"/>
+        <v>58.7</v>
+      </c>
+      <c r="I38" s="6" t="n">
+        <v>0.03213831121723015</v>
+      </c>
       <c r="J38" s="3" t="n">
-        <v>6369</v>
+        <v>20962</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>2999</v>
+        <v>40377</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>flaxseed</t>
+          <t>flax</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
@@ -1804,12 +1810,12 @@
       <c r="E39" s="4" t="n">
         <v>0.97</v>
       </c>
-      <c r="F39" s="4" t="inlineStr"/>
-      <c r="G39" s="4" t="inlineStr"/>
+      <c r="F39" s="4" t="n"/>
+      <c r="G39" s="4" t="n"/>
       <c r="H39" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I39" s="6" t="inlineStr"/>
+      <c r="I39" s="6" t="n"/>
       <c r="J39" s="3" t="n">
         <v>6369</v>
       </c>
@@ -1820,75 +1826,69 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>vitamin_d</t>
+          <t>flaxseed</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C40" s="4" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>0.79</v>
+        <v>0.72</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="F40" s="4" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="G40" s="4" t="n">
-        <v>1.16</v>
-      </c>
+        <v>0.97</v>
+      </c>
+      <c r="F40" s="4" t="n"/>
+      <c r="G40" s="4" t="n"/>
       <c r="H40" s="5" t="n">
-        <v>77.7</v>
-      </c>
-      <c r="I40" s="6" t="n">
-        <v>0.0006283901271037934</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I40" s="6" t="n"/>
       <c r="J40" s="3" t="n">
-        <v>1049317</v>
+        <v>6369</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>55897</v>
+        <v>2999</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>vitamin_e</t>
+          <t>vitamin_d</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C41" s="4" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>0.74</v>
+        <v>0.79</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>1.01</v>
+        <v>0.91</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>0.52</v>
+        <v>0.62</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>1.43</v>
+        <v>1.16</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>71.2</v>
+        <v>77.7</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>0.06550103119355563</v>
+        <v>0.0006283901271037919</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>235680</v>
+        <v>1049317</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>28952</v>
+        <v>55897</v>
       </c>
     </row>
     <row r="42">
@@ -1919,7 +1919,7 @@
         <v>86.8</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>0.2027909138053139</v>
+        <v>0.2027909138053141</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>250180</v>
@@ -1956,7 +1956,7 @@
         <v>91.2</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>0.4716969629243402</v>
+        <v>0.4716969629243401</v>
       </c>
       <c r="J43" s="3" t="n">
         <v>287201</v>
@@ -1968,69 +1968,69 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>magnesium</t>
+          <t>calcium</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C44" s="4" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="D44" s="4" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F44" s="4" t="n">
         <v>0.79</v>
       </c>
-      <c r="E44" s="4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="F44" s="4" t="inlineStr"/>
-      <c r="G44" s="4" t="inlineStr"/>
+      <c r="G44" s="4" t="n">
+        <v>1.02</v>
+      </c>
       <c r="H44" s="5" t="n">
-        <v>62.4</v>
-      </c>
-      <c r="I44" s="6" t="inlineStr"/>
+        <v>73.59999999999999</v>
+      </c>
+      <c r="I44" s="6" t="n">
+        <v>1.699397376993426e-06</v>
+      </c>
       <c r="J44" s="3" t="n">
-        <v>69324</v>
+        <v>871662</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>9766</v>
+        <v>74218</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>calcium</t>
+          <t>magnesium</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C45" s="4" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>0.88</v>
+        <v>0.79</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="F45" s="4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G45" s="4" t="n">
-        <v>1.05</v>
-      </c>
+        <v>1.06</v>
+      </c>
+      <c r="F45" s="4" t="n"/>
+      <c r="G45" s="4" t="n"/>
       <c r="H45" s="5" t="n">
-        <v>77.8</v>
-      </c>
-      <c r="I45" s="6" t="n">
-        <v>0.0006986996017865496</v>
-      </c>
+        <v>62.4</v>
+      </c>
+      <c r="I45" s="6" t="n"/>
       <c r="J45" s="3" t="n">
-        <v>871838</v>
+        <v>69324</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>74278</v>
+        <v>9766</v>
       </c>
     </row>
     <row r="46">
@@ -2061,7 +2061,7 @@
         <v>83</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>0.5612991451474079</v>
+        <v>0.5612991451474082</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>512782</v>
@@ -2098,7 +2098,7 @@
         <v>45.9</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>0.4259906328747249</v>
+        <v>0.4259906328747247</v>
       </c>
       <c r="J47" s="3" t="n">
         <v>872194</v>
@@ -2135,7 +2135,7 @@
         <v>84.09999999999999</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>0.1938542056483222</v>
+        <v>0.193854205648322</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>2671430</v>
@@ -2162,12 +2162,12 @@
       <c r="E49" s="4" t="n">
         <v>1.5</v>
       </c>
-      <c r="F49" s="4" t="inlineStr"/>
-      <c r="G49" s="4" t="inlineStr"/>
+      <c r="F49" s="4" t="n"/>
+      <c r="G49" s="4" t="n"/>
       <c r="H49" s="5" t="n">
         <v>91.8</v>
       </c>
-      <c r="I49" s="6" t="inlineStr"/>
+      <c r="I49" s="6" t="n"/>
       <c r="J49" s="3" t="n">
         <v>5048</v>
       </c>
@@ -2203,7 +2203,7 @@
         <v>65</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>0.7255960351225048</v>
+        <v>0.7255960351225049</v>
       </c>
       <c r="J50" s="3" t="n">
         <v>175826</v>
@@ -2240,7 +2240,7 @@
         <v>91</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>0.7631578999845161</v>
+        <v>0.7631578999845166</v>
       </c>
       <c r="J51" s="3" t="n">
         <v>1631244</v>
@@ -2267,12 +2267,12 @@
       <c r="E52" s="4" t="n">
         <v>1.34</v>
       </c>
-      <c r="F52" s="4" t="inlineStr"/>
-      <c r="G52" s="4" t="inlineStr"/>
+      <c r="F52" s="4" t="n"/>
+      <c r="G52" s="4" t="n"/>
       <c r="H52" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I52" s="6" t="inlineStr"/>
+      <c r="I52" s="6" t="n"/>
       <c r="J52" s="3" t="n">
         <v>90630</v>
       </c>
@@ -2283,69 +2283,69 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>glucosamine</t>
+          <t>conjugated_linoleic_acid</t>
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C53" s="4" t="n">
         <v>1.06</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="F53" s="4" t="inlineStr"/>
-      <c r="G53" s="4" t="inlineStr"/>
+        <v>1.22</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>1.82</v>
+      </c>
       <c r="H53" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" s="6" t="inlineStr"/>
+        <v>62</v>
+      </c>
+      <c r="I53" s="6" t="n">
+        <v>0.4225544208553845</v>
+      </c>
       <c r="J53" s="3" t="n">
-        <v>41082</v>
+        <v>380443</v>
       </c>
       <c r="K53" s="3" t="n">
-        <v>5341</v>
+        <v>17329</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>conjugated_linoleic_acid</t>
+          <t>glucosamine</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C54" s="4" t="n">
         <v>1.06</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="F54" s="4" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="G54" s="4" t="n">
-        <v>1.82</v>
-      </c>
+        <v>1.21</v>
+      </c>
+      <c r="F54" s="4" t="n"/>
+      <c r="G54" s="4" t="n"/>
       <c r="H54" s="5" t="n">
-        <v>62</v>
-      </c>
-      <c r="I54" s="6" t="n">
-        <v>0.4225544208553845</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I54" s="6" t="n"/>
       <c r="J54" s="3" t="n">
-        <v>380443</v>
+        <v>41082</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>17329</v>
+        <v>5341</v>
       </c>
     </row>
     <row r="55">
@@ -2366,12 +2366,12 @@
       <c r="E55" s="4" t="n">
         <v>1.52</v>
       </c>
-      <c r="F55" s="4" t="inlineStr"/>
-      <c r="G55" s="4" t="inlineStr"/>
+      <c r="F55" s="4" t="n"/>
+      <c r="G55" s="4" t="n"/>
       <c r="H55" s="5" t="n">
         <v>82.8</v>
       </c>
-      <c r="I55" s="6" t="inlineStr"/>
+      <c r="I55" s="6" t="n"/>
       <c r="J55" s="3" t="n">
         <v>164504</v>
       </c>
@@ -2386,34 +2386,34 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C56" s="4" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>0.95</v>
+        <v>0.99</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="H56" s="5" t="n">
-        <v>86.59999999999999</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>0.7478766568479693</v>
+        <v>0.9936223155021588</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>29487</v>
+        <v>29311</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>5481</v>
+        <v>5421</v>
       </c>
     </row>
     <row r="57">
@@ -2444,7 +2444,7 @@
         <v>80</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>0.533827914910584</v>
+        <v>0.5338279149105838</v>
       </c>
       <c r="J57" s="3" t="n">
         <v>385425</v>
@@ -2456,75 +2456,75 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>red_meat</t>
+          <t>alcohol</t>
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>34</v>
+        <v>185</v>
       </c>
       <c r="C58" s="4" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>0.95</v>
+        <v>1.04</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>1.85</v>
+        <v>1.47</v>
       </c>
       <c r="H58" s="5" t="n">
-        <v>86.5</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>4.523365894739169e-11</v>
+        <v>4.727934742268639e-31</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>1178141</v>
+        <v>16045202</v>
       </c>
       <c r="K58" s="3" t="n">
-        <v>60075</v>
+        <v>1276703</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>alcohol</t>
+          <t>red_meat</t>
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>191</v>
+        <v>34</v>
       </c>
       <c r="C59" s="4" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="E59" s="4" t="n">
         <v>1.42</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>0.86</v>
+        <v>0.95</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>2.17</v>
+        <v>1.85</v>
       </c>
       <c r="H59" s="5" t="n">
-        <v>98.3</v>
+        <v>86.5</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>6.130987900347651e-06</v>
+        <v>4.52336589473918e-11</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>16169285</v>
+        <v>1178141</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>1285264</v>
+        <v>60075</v>
       </c>
     </row>
     <row r="60">
@@ -2534,34 +2534,28 @@
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C60" s="4" t="n">
-        <v>1.45</v>
+        <v>1.74</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="F60" s="4" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="G60" s="4" t="n">
-        <v>23.42</v>
-      </c>
+        <v>2.42</v>
+      </c>
+      <c r="F60" s="4" t="n"/>
+      <c r="G60" s="4" t="n"/>
       <c r="H60" s="5" t="n">
-        <v>38</v>
-      </c>
-      <c r="I60" s="6" t="n">
-        <v>0.2551749856537071</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I60" s="6" t="n"/>
       <c r="J60" s="3" t="n">
-        <v>5439</v>
+        <v>2476</v>
       </c>
       <c r="K60" s="3" t="n">
-        <v>2664</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="61">
@@ -2582,12 +2576,12 @@
       <c r="E61" s="4" t="n">
         <v>5.61</v>
       </c>
-      <c r="F61" s="4" t="inlineStr"/>
-      <c r="G61" s="4" t="inlineStr"/>
+      <c r="F61" s="4" t="n"/>
+      <c r="G61" s="4" t="n"/>
       <c r="H61" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I61" s="6" t="inlineStr"/>
+      <c r="I61" s="6" t="n"/>
       <c r="J61" s="3" t="n">
         <v>370</v>
       </c>
@@ -2613,12 +2607,12 @@
       <c r="E62" s="4" t="n">
         <v>4.78</v>
       </c>
-      <c r="F62" s="4" t="inlineStr"/>
-      <c r="G62" s="4" t="inlineStr"/>
+      <c r="F62" s="4" t="n"/>
+      <c r="G62" s="4" t="n"/>
       <c r="H62" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I62" s="6" t="inlineStr"/>
+      <c r="I62" s="6" t="n"/>
       <c r="J62" s="3" t="n">
         <v>718</v>
       </c>

--- a/Plot/exposures_meta_analysis_breast_dietary.xlsx
+++ b/Plot/exposures_meta_analysis_breast_dietary.xlsx
@@ -714,7 +714,7 @@
         <v>88.5</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.09173584726167605</v>
+        <v>0.09173584726167613</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>90844</v>
@@ -912,7 +912,7 @@
         <v>54.6</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.2487315066792918</v>
+        <v>0.2487315066792916</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>43927</v>
@@ -949,7 +949,7 @@
         <v>76.09999999999999</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.001205141873155634</v>
+        <v>0.001205141873155637</v>
       </c>
       <c r="J14" s="3" t="n">
         <v>1061834</v>
@@ -986,7 +986,7 @@
         <v>64.5</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.4864450605937343</v>
+        <v>0.4864450605937342</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>238479</v>
@@ -1023,7 +1023,7 @@
         <v>86</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.01777472721809745</v>
+        <v>0.01777472721809741</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>392499</v>
@@ -1159,7 +1159,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>5.667201636158433e-06</v>
+        <v>5.667201636158439e-06</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>990467</v>
@@ -1264,7 +1264,7 @@
         <v>87.40000000000001</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.05582483881549636</v>
+        <v>0.05582483881549634</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>508253</v>
@@ -1301,7 +1301,7 @@
         <v>86.09999999999999</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>4.315818448979679e-05</v>
+        <v>4.31581844897966e-05</v>
       </c>
       <c r="J24" s="3" t="n">
         <v>273560</v>
@@ -1381,118 +1381,112 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>vitamin_e</t>
+          <t>beta-carotene</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.63</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.4</v>
+        <v>0.49</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>77.7</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.004128823967049899</v>
+        <v>0.01807598378940585</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>303677</v>
+        <v>1684061</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>30794</v>
+        <v>114896</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>beta-carotene</t>
+          <t>mediterranean_diet</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>0.76</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.49</v>
+        <v>0.54</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>82.59999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.01807598378940583</v>
+        <v>4.147592651637323e-05</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>1684061</v>
+        <v>639823</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>114896</v>
+        <v>40922</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>mediterranean_diet</t>
+          <t>bcaas</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="F29" s="4" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="G29" s="4" t="n">
-        <v>1.08</v>
-      </c>
+        <v>1.48</v>
+      </c>
+      <c r="F29" s="4" t="n"/>
+      <c r="G29" s="4" t="n"/>
       <c r="H29" s="5" t="n">
-        <v>87.2</v>
-      </c>
-      <c r="I29" s="6" t="n">
-        <v>4.147592651637327e-05</v>
-      </c>
+        <v>92.8</v>
+      </c>
+      <c r="I29" s="6" t="n"/>
       <c r="J29" s="3" t="n">
-        <v>639823</v>
+        <v>197211</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>40922</v>
+        <v>10396</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>bcaas</t>
+          <t>isoleucine</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
@@ -1523,7 +1517,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>isoleucine</t>
+          <t>leucine</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
@@ -1554,63 +1548,69 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>leucine</t>
+          <t>cod_liver_oil</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
         <v>2</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.4</v>
+        <v>0.68</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1.48</v>
+        <v>0.9</v>
       </c>
       <c r="F32" s="4" t="n"/>
       <c r="G32" s="4" t="n"/>
       <c r="H32" s="5" t="n">
-        <v>92.8</v>
+        <v>0</v>
       </c>
       <c r="I32" s="6" t="n"/>
       <c r="J32" s="3" t="n">
-        <v>197211</v>
+        <v>4001</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>10396</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>cod_liver_oil</t>
+          <t>vitamin_e</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>0.78</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F33" s="4" t="n"/>
-      <c r="G33" s="4" t="n"/>
+        <v>0.89</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>1.28</v>
+      </c>
       <c r="H33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="6" t="n"/>
+        <v>76.2</v>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>0.01267231695120217</v>
+      </c>
       <c r="J33" s="3" t="n">
-        <v>4001</v>
+        <v>332971</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>1731</v>
+        <v>34602</v>
       </c>
     </row>
     <row r="34">
@@ -1672,7 +1672,7 @@
         <v>57</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>0.5607534123225346</v>
+        <v>0.5607534123225345</v>
       </c>
       <c r="J35" s="3" t="n">
         <v>87065</v>
@@ -1709,7 +1709,7 @@
         <v>81</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>0.01389915282783274</v>
+        <v>0.01389915282783273</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>248595</v>
@@ -1746,7 +1746,7 @@
         <v>90.8</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>0.5897124894853758</v>
+        <v>0.5897124894853762</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>190614</v>
@@ -1783,7 +1783,7 @@
         <v>58.7</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>0.03213831121723015</v>
+        <v>0.0321383112172301</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>20962</v>
@@ -1882,7 +1882,7 @@
         <v>77.7</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>0.0006283901271037919</v>
+        <v>0.0006283901271037934</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>1049317</v>
@@ -1919,7 +1919,7 @@
         <v>86.8</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>0.2027909138053141</v>
+        <v>0.2027909138053139</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>250180</v>
@@ -1956,7 +1956,7 @@
         <v>91.2</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>0.4716969629243401</v>
+        <v>0.4716969629243402</v>
       </c>
       <c r="J43" s="3" t="n">
         <v>287201</v>
@@ -1993,7 +1993,7 @@
         <v>73.59999999999999</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>1.699397376993426e-06</v>
+        <v>1.699397376993427e-06</v>
       </c>
       <c r="J44" s="3" t="n">
         <v>871662</v>
@@ -2061,7 +2061,7 @@
         <v>83</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>0.5612991451474082</v>
+        <v>0.5612991451474079</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>512782</v>
@@ -2098,7 +2098,7 @@
         <v>45.9</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>0.4259906328747247</v>
+        <v>0.4259906328747249</v>
       </c>
       <c r="J47" s="3" t="n">
         <v>872194</v>
@@ -2135,7 +2135,7 @@
         <v>84.09999999999999</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>0.193854205648322</v>
+        <v>0.1938542056483222</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>2671430</v>
@@ -2203,7 +2203,7 @@
         <v>65</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>0.7255960351225049</v>
+        <v>0.7255960351225048</v>
       </c>
       <c r="J50" s="3" t="n">
         <v>175826</v>
@@ -2240,7 +2240,7 @@
         <v>91</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>0.7631578999845166</v>
+        <v>0.7631578999845161</v>
       </c>
       <c r="J51" s="3" t="n">
         <v>1631244</v>
@@ -2407,7 +2407,7 @@
         <v>86.90000000000001</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>0.9936223155021588</v>
+        <v>0.9936223155021582</v>
       </c>
       <c r="J56" s="3" t="n">
         <v>29311</v>
@@ -2444,7 +2444,7 @@
         <v>80</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>0.5338279149105838</v>
+        <v>0.533827914910584</v>
       </c>
       <c r="J57" s="3" t="n">
         <v>385425</v>
@@ -2481,7 +2481,7 @@
         <v>89.59999999999999</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>4.727934742268639e-31</v>
+        <v>4.727934742268441e-31</v>
       </c>
       <c r="J58" s="3" t="n">
         <v>16045202</v>
@@ -2518,7 +2518,7 @@
         <v>86.5</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>4.52336589473918e-11</v>
+        <v>4.523365894739169e-11</v>
       </c>
       <c r="J59" s="3" t="n">
         <v>1178141</v>

--- a/Plot/exposures_meta_analysis_breast_dietary.xlsx
+++ b/Plot/exposures_meta_analysis_breast_dietary.xlsx
@@ -1455,38 +1455,44 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>bcaas</t>
+          <t>vitamin_e</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="D29" s="4" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="F29" s="4" t="n">
         <v>0.4</v>
       </c>
-      <c r="E29" s="4" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="F29" s="4" t="n"/>
-      <c r="G29" s="4" t="n"/>
+      <c r="G29" s="4" t="n">
+        <v>1.45</v>
+      </c>
       <c r="H29" s="5" t="n">
-        <v>92.8</v>
-      </c>
-      <c r="I29" s="6" t="n"/>
+        <v>79.40000000000001</v>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>0.01143489138791379</v>
+      </c>
       <c r="J29" s="3" t="n">
-        <v>197211</v>
+        <v>302435</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>10396</v>
+        <v>30228</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>isoleucine</t>
+          <t>bcaas</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
@@ -1517,7 +1523,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>leucine</t>
+          <t>isoleucine</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
@@ -1548,69 +1554,63 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>cod_liver_oil</t>
+          <t>leucine</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
         <v>2</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.68</v>
+        <v>0.4</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.9</v>
+        <v>1.48</v>
       </c>
       <c r="F32" s="4" t="n"/>
       <c r="G32" s="4" t="n"/>
       <c r="H32" s="5" t="n">
-        <v>0</v>
+        <v>92.8</v>
       </c>
       <c r="I32" s="6" t="n"/>
       <c r="J32" s="3" t="n">
-        <v>4001</v>
+        <v>197211</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>1731</v>
+        <v>10396</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>vitamin_e</t>
+          <t>cod_liver_oil</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>0.78</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="F33" s="4" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="G33" s="4" t="n">
-        <v>1.28</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="4" t="n"/>
       <c r="H33" s="5" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="I33" s="6" t="n">
-        <v>0.01267231695120217</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I33" s="6" t="n"/>
       <c r="J33" s="3" t="n">
-        <v>332971</v>
+        <v>4001</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>34602</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="34">
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C48" s="4" t="n">
         <v>0.97</v>
@@ -2126,22 +2126,22 @@
         <v>1.02</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="H48" s="5" t="n">
-        <v>84.09999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>0.1938542056483222</v>
+        <v>0.1742603566952903</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>2671430</v>
+        <v>2055428</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>171298</v>
+        <v>91218</v>
       </c>
     </row>
     <row r="49">
@@ -2219,34 +2219,34 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C51" s="4" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>0.96</v>
+        <v>0.93</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="H51" s="5" t="n">
-        <v>91</v>
+        <v>91.7</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>0.7631578999845161</v>
+        <v>0.7691629815442262</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>1631244</v>
+        <v>1181650</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>201438</v>
+        <v>65433</v>
       </c>
     </row>
     <row r="52">

--- a/Plot/exposures_meta_analysis_breast_dietary.xlsx
+++ b/Plot/exposures_meta_analysis_breast_dietary.xlsx
@@ -609,7 +609,7 @@
         <v>73.09999999999999</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.1770583184646601</v>
+        <v>0.1770583184646593</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>52399</v>
@@ -875,7 +875,7 @@
         <v>88.7</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.09471360956321104</v>
+        <v>0.0947136095632109</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>38506</v>
@@ -912,7 +912,7 @@
         <v>54.6</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.2487315066792916</v>
+        <v>0.2487315066792917</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>43927</v>
@@ -986,7 +986,7 @@
         <v>64.5</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.4864450605937342</v>
+        <v>0.4864450605937327</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>238479</v>
@@ -1023,7 +1023,7 @@
         <v>86</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.01777472721809741</v>
+        <v>0.01777472721809728</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>392499</v>
@@ -1156,10 +1156,10 @@
         <v>1.21</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>81.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>5.667201636158439e-06</v>
+        <v>4.552460424870794e-06</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>990467</v>
@@ -1301,7 +1301,7 @@
         <v>86.09999999999999</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>4.31581844897966e-05</v>
+        <v>4.315818448979668e-05</v>
       </c>
       <c r="J24" s="3" t="n">
         <v>273560</v>
@@ -1338,7 +1338,7 @@
         <v>91.09999999999999</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.03117076126282999</v>
+        <v>0.03117076126282993</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>919838</v>
@@ -1381,143 +1381,143 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>beta-carotene</t>
+          <t>mediterranean_diet</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>0.76</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.49</v>
+        <v>0.54</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>82.59999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.01807598378940585</v>
+        <v>4.147592651637335e-05</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>1684061</v>
+        <v>639823</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>114896</v>
+        <v>40922</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>mediterranean_diet</t>
+          <t>vitamin_e</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>0.76</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.83</v>
+        <v>0.91</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.54</v>
+        <v>0.4</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>1.08</v>
+        <v>1.44</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>87.2</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>4.147592651637323e-05</v>
+        <v>0.01158768167145667</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>639823</v>
+        <v>302435</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>40922</v>
+        <v>30228</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>vitamin_e</t>
+          <t>bcaas</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.64</v>
+        <v>0.4</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="F29" s="4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G29" s="4" t="n">
-        <v>1.45</v>
-      </c>
+        <v>1.48</v>
+      </c>
+      <c r="F29" s="4" t="n"/>
+      <c r="G29" s="4" t="n"/>
       <c r="H29" s="5" t="n">
-        <v>79.40000000000001</v>
-      </c>
-      <c r="I29" s="6" t="n">
-        <v>0.01143489138791379</v>
-      </c>
+        <v>92.8</v>
+      </c>
+      <c r="I29" s="6" t="n"/>
       <c r="J29" s="3" t="n">
-        <v>302435</v>
+        <v>197211</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>30228</v>
+        <v>10396</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>bcaas</t>
+          <t>beta-carotene</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>0.77</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.4</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="F30" s="4" t="n"/>
-      <c r="G30" s="4" t="n"/>
+        <v>0.85</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>1.18</v>
+      </c>
       <c r="H30" s="5" t="n">
-        <v>92.8</v>
-      </c>
-      <c r="I30" s="6" t="n"/>
+        <v>82.59999999999999</v>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>0.01839446183459994</v>
+      </c>
       <c r="J30" s="3" t="n">
-        <v>197211</v>
+        <v>1684061</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>10396</v>
+        <v>114896</v>
       </c>
     </row>
     <row r="31">
@@ -1672,7 +1672,7 @@
         <v>57</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>0.5607534123225345</v>
+        <v>0.5607534123225351</v>
       </c>
       <c r="J35" s="3" t="n">
         <v>87065</v>
@@ -1709,7 +1709,7 @@
         <v>81</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>0.01389915282783273</v>
+        <v>0.01389915282783274</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>248595</v>
@@ -1746,7 +1746,7 @@
         <v>90.8</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>0.5897124894853762</v>
+        <v>0.5897124894853758</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>190614</v>
@@ -1783,7 +1783,7 @@
         <v>58.7</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>0.0321383112172301</v>
+        <v>0.03213831121723015</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>20962</v>
@@ -1882,7 +1882,7 @@
         <v>77.7</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>0.0006283901271037934</v>
+        <v>0.0006283901271037745</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>1049317</v>
@@ -1919,7 +1919,7 @@
         <v>86.8</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>0.2027909138053139</v>
+        <v>0.2027909138053141</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>250180</v>
@@ -1993,7 +1993,7 @@
         <v>73.59999999999999</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>1.699397376993427e-06</v>
+        <v>1.699397376993572e-06</v>
       </c>
       <c r="J44" s="3" t="n">
         <v>871662</v>
@@ -2098,7 +2098,7 @@
         <v>45.9</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>0.4259906328747249</v>
+        <v>0.4259906328747333</v>
       </c>
       <c r="J47" s="3" t="n">
         <v>872194</v>
@@ -2135,7 +2135,7 @@
         <v>84.2</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>0.1742603566952903</v>
+        <v>0.1742603566952905</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>2055428</v>
@@ -2240,7 +2240,7 @@
         <v>91.7</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>0.7691629815442262</v>
+        <v>0.7691629815442271</v>
       </c>
       <c r="J51" s="3" t="n">
         <v>1181650</v>
@@ -2308,7 +2308,7 @@
         <v>62</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>0.4225544208553845</v>
+        <v>0.4225544208553847</v>
       </c>
       <c r="J53" s="3" t="n">
         <v>380443</v>
@@ -2407,7 +2407,7 @@
         <v>86.90000000000001</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>0.9936223155021582</v>
+        <v>0.993622315502159</v>
       </c>
       <c r="J56" s="3" t="n">
         <v>29311</v>
@@ -2444,7 +2444,7 @@
         <v>80</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>0.533827914910584</v>
+        <v>0.5338279149105822</v>
       </c>
       <c r="J57" s="3" t="n">
         <v>385425</v>
@@ -2481,7 +2481,7 @@
         <v>89.59999999999999</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>4.727934742268441e-31</v>
+        <v>4.744516340473689e-31</v>
       </c>
       <c r="J58" s="3" t="n">
         <v>16045202</v>
@@ -2518,7 +2518,7 @@
         <v>86.5</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>4.523365894739169e-11</v>
+        <v>4.523365894739185e-11</v>
       </c>
       <c r="J59" s="3" t="n">
         <v>1178141</v>

--- a/Plot/exposures_meta_analysis_breast_dietary.xlsx
+++ b/Plot/exposures_meta_analysis_breast_dietary.xlsx
@@ -714,7 +714,7 @@
         <v>88.5</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.09173584726167613</v>
+        <v>0.09173584726167605</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>90844</v>
@@ -850,149 +850,149 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>vitamin_b12</t>
+          <t>zinc</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>0.65</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.44</v>
+        <v>0.49</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.95</v>
+        <v>0.88</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.17</v>
+        <v>0.26</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>2.42</v>
+        <v>1.61</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>88.7</v>
+        <v>54.6</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.0947136095632109</v>
+        <v>0.2487315066792918</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>38506</v>
+        <v>43927</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>8006</v>
+        <v>7652</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>zinc</t>
+          <t>lutein</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.49</v>
+        <v>0.55</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.88</v>
+        <v>0.8</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.26</v>
+        <v>0.37</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.61</v>
+        <v>1.2</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>54.6</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.2487315066792917</v>
+        <v>0.001205141873155634</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>43927</v>
+        <v>1061834</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>7652</v>
+        <v>45572</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>lutein</t>
+          <t>omega-3_fatty_acids</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="E14" s="4" t="n">
         <v>0.8</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.37</v>
+        <v>0.39</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>76.09999999999999</v>
+        <v>64.5</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.001205141873155637</v>
+        <v>0.4864450605937326</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>1061834</v>
+        <v>238479</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>45572</v>
+        <v>7644</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>omega-3_fatty_acids</t>
+          <t>vitamin_b12</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>0.67</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.57</v>
+        <v>0.44</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.8</v>
+        <v>1.02</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.39</v>
+        <v>0.14</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.16</v>
+        <v>3.16</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>64.5</v>
+        <v>90.5</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.4864450605937327</v>
+        <v>0.1259969123482508</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>238479</v>
+        <v>38106</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>7644</v>
+        <v>7877</v>
       </c>
     </row>
     <row r="16">
@@ -1023,7 +1023,7 @@
         <v>86</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.01777472721809728</v>
+        <v>0.01777472721809727</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>392499</v>
@@ -1138,34 +1138,34 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>0.65</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>82</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>4.552460424870794e-06</v>
+        <v>1.026480004102468e-05</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>990467</v>
+        <v>990067</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>46628</v>
+        <v>46499</v>
       </c>
     </row>
     <row r="21">
@@ -1264,7 +1264,7 @@
         <v>87.40000000000001</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.05582483881549634</v>
+        <v>0.05582483881549636</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>508253</v>
@@ -1301,7 +1301,7 @@
         <v>86.09999999999999</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>4.315818448979668e-05</v>
+        <v>4.315818448979673e-05</v>
       </c>
       <c r="J24" s="3" t="n">
         <v>273560</v>
@@ -1338,7 +1338,7 @@
         <v>91.09999999999999</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.03117076126282993</v>
+        <v>0.03117076126283006</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>919838</v>
@@ -1406,7 +1406,7 @@
         <v>87.2</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>4.147592651637335e-05</v>
+        <v>4.147592651637327e-05</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>639823</v>
@@ -1443,7 +1443,7 @@
         <v>79.40000000000001</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.01158768167145667</v>
+        <v>0.01158768167145665</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>302435</v>
@@ -1672,7 +1672,7 @@
         <v>57</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>0.5607534123225351</v>
+        <v>0.5607534123225348</v>
       </c>
       <c r="J35" s="3" t="n">
         <v>87065</v>
@@ -1709,7 +1709,7 @@
         <v>81</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>0.01389915282783274</v>
+        <v>0.01389915282783272</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>248595</v>
@@ -1746,7 +1746,7 @@
         <v>90.8</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>0.5897124894853758</v>
+        <v>0.5897124894853759</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>190614</v>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C41" s="4" t="n">
         <v>0.85</v>
@@ -1870,25 +1870,25 @@
         <v>0.79</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="F41" s="4" t="n">
         <v>0.62</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>77.7</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>0.0006283901271037745</v>
+        <v>0.001225883425616299</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>1049317</v>
+        <v>1048907</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>55897</v>
+        <v>55763</v>
       </c>
     </row>
     <row r="42">
@@ -1956,7 +1956,7 @@
         <v>91.2</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>0.4716969629243402</v>
+        <v>0.47169696292434</v>
       </c>
       <c r="J43" s="3" t="n">
         <v>287201</v>
@@ -1993,7 +1993,7 @@
         <v>73.59999999999999</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>1.699397376993572e-06</v>
+        <v>1.699397376993577e-06</v>
       </c>
       <c r="J44" s="3" t="n">
         <v>871662</v>
@@ -2061,7 +2061,7 @@
         <v>83</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>0.5612991451474079</v>
+        <v>0.5612991451474082</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>512782</v>
@@ -2098,7 +2098,7 @@
         <v>45.9</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>0.4259906328747333</v>
+        <v>0.4259906328747331</v>
       </c>
       <c r="J47" s="3" t="n">
         <v>872194</v>
@@ -2135,7 +2135,7 @@
         <v>84.2</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>0.1742603566952905</v>
+        <v>0.1742603566952906</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>2055428</v>
@@ -2203,7 +2203,7 @@
         <v>65</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>0.7255960351225048</v>
+        <v>0.725596035122505</v>
       </c>
       <c r="J50" s="3" t="n">
         <v>175826</v>
@@ -2308,7 +2308,7 @@
         <v>62</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>0.4225544208553847</v>
+        <v>0.4225544208553849</v>
       </c>
       <c r="J53" s="3" t="n">
         <v>380443</v>
@@ -2407,7 +2407,7 @@
         <v>86.90000000000001</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>0.993622315502159</v>
+        <v>0.9936223155021582</v>
       </c>
       <c r="J56" s="3" t="n">
         <v>29311</v>
@@ -2460,34 +2460,34 @@
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C58" s="4" t="n">
         <v>1.24</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="F58" s="4" t="n">
         <v>1.04</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="H58" s="5" t="n">
-        <v>89.59999999999999</v>
+        <v>89.7</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>4.744516340473689e-31</v>
+        <v>3.221688720496117e-31</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>16045202</v>
+        <v>16035924</v>
       </c>
       <c r="K58" s="3" t="n">
-        <v>1276703</v>
+        <v>1275429</v>
       </c>
     </row>
     <row r="59">
@@ -2518,7 +2518,7 @@
         <v>86.5</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>4.523365894739185e-11</v>
+        <v>4.52336589473918e-11</v>
       </c>
       <c r="J59" s="3" t="n">
         <v>1178141</v>

--- a/Plot/exposures_meta_analysis_breast_dietary.xlsx
+++ b/Plot/exposures_meta_analysis_breast_dietary.xlsx
@@ -1418,112 +1418,106 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>vitamin_e</t>
+          <t>bcaas</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.64</v>
+        <v>0.4</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="F28" s="4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G28" s="4" t="n">
-        <v>1.44</v>
-      </c>
+        <v>1.48</v>
+      </c>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
       <c r="H28" s="5" t="n">
-        <v>79.40000000000001</v>
-      </c>
-      <c r="I28" s="6" t="n">
-        <v>0.01158768167145665</v>
-      </c>
+        <v>92.8</v>
+      </c>
+      <c r="I28" s="6" t="n"/>
       <c r="J28" s="3" t="n">
-        <v>302435</v>
+        <v>197211</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>30228</v>
+        <v>10396</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>bcaas</t>
+          <t>beta-carotene</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>0.77</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.4</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="F29" s="4" t="n"/>
-      <c r="G29" s="4" t="n"/>
+        <v>0.85</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>1.18</v>
+      </c>
       <c r="H29" s="5" t="n">
-        <v>92.8</v>
-      </c>
-      <c r="I29" s="6" t="n"/>
+        <v>82.59999999999999</v>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>0.01839446183459994</v>
+      </c>
       <c r="J29" s="3" t="n">
-        <v>197211</v>
+        <v>1684061</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>10396</v>
+        <v>114896</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>beta-carotene</t>
+          <t>isoleucine</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>0.77</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="F30" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G30" s="4" t="n">
-        <v>1.18</v>
-      </c>
+        <v>1.48</v>
+      </c>
+      <c r="F30" s="4" t="n"/>
+      <c r="G30" s="4" t="n"/>
       <c r="H30" s="5" t="n">
-        <v>82.59999999999999</v>
-      </c>
-      <c r="I30" s="6" t="n">
-        <v>0.01839446183459994</v>
-      </c>
+        <v>92.8</v>
+      </c>
+      <c r="I30" s="6" t="n"/>
       <c r="J30" s="3" t="n">
-        <v>1684061</v>
+        <v>197211</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>114896</v>
+        <v>10396</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>isoleucine</t>
+          <t>leucine</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
@@ -1554,168 +1548,174 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>leucine</t>
+          <t>cod_liver_oil</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
         <v>2</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.4</v>
+        <v>0.68</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1.48</v>
+        <v>0.9</v>
       </c>
       <c r="F32" s="4" t="n"/>
       <c r="G32" s="4" t="n"/>
       <c r="H32" s="5" t="n">
-        <v>92.8</v>
+        <v>0</v>
       </c>
       <c r="I32" s="6" t="n"/>
       <c r="J32" s="3" t="n">
-        <v>197211</v>
+        <v>4001</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>10396</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>cod_liver_oil</t>
+          <t>betaine</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
         <v>2</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.68</v>
+        <v>0.5</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.9</v>
+        <v>1.25</v>
       </c>
       <c r="F33" s="4" t="n"/>
       <c r="G33" s="4" t="n"/>
       <c r="H33" s="5" t="n">
-        <v>0</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I33" s="6" t="n"/>
       <c r="J33" s="3" t="n">
-        <v>4001</v>
+        <v>76198</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>1731</v>
+        <v>4797</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>betaine</t>
+          <t>miso</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="F34" s="4" t="n"/>
-      <c r="G34" s="4" t="n"/>
+        <v>1.13</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>33.61</v>
+      </c>
       <c r="H34" s="5" t="n">
-        <v>88.40000000000001</v>
-      </c>
-      <c r="I34" s="6" t="n"/>
+        <v>57</v>
+      </c>
+      <c r="I34" s="6" t="n">
+        <v>0.5607534123225348</v>
+      </c>
       <c r="J34" s="3" t="n">
-        <v>76198</v>
+        <v>87065</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>4797</v>
+        <v>751</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>miso</t>
+          <t>olive</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>0.8</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>1.13</v>
+        <v>0.92</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.02</v>
+        <v>0.51</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>33.61</v>
+        <v>1.24</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>0.5607534123225348</v>
+        <v>0.01389915282783272</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>87065</v>
+        <v>248595</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>751</v>
+        <v>16870</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>olive</t>
+          <t>vitamin_e</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.92</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F36" s="4" t="n">
         <v>0.51</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>81</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>0.01389915282783272</v>
+        <v>0.001124686483274099</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>248595</v>
+        <v>235680</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>16870</v>
+        <v>28952</v>
       </c>
     </row>
     <row r="37">

--- a/Plot/exposures_meta_analysis_breast_dietary.xlsx
+++ b/Plot/exposures_meta_analysis_breast_dietary.xlsx
@@ -1134,143 +1134,143 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>folic_acid</t>
+          <t>mineral_supplements</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>0.73</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.65</v>
+        <v>0.43</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>1.22</v>
-      </c>
+        <v>1.17</v>
+      </c>
+      <c r="F20" s="4" t="n"/>
+      <c r="G20" s="4" t="n"/>
       <c r="H20" s="5" t="n">
-        <v>82.09999999999999</v>
-      </c>
-      <c r="I20" s="6" t="n">
-        <v>1.026480004102468e-05</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I20" s="6" t="n"/>
       <c r="J20" s="3" t="n">
-        <v>990067</v>
+        <v>836</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>46499</v>
+        <v>312</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>mineral_supplements</t>
+          <t>choline</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="F21" s="4" t="n"/>
-      <c r="G21" s="4" t="n"/>
+        <v>1.21</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>361.92</v>
+      </c>
       <c r="H21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="6" t="n"/>
+        <v>93.5</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>0.160920736648293</v>
+      </c>
       <c r="J21" s="3" t="n">
-        <v>836</v>
+        <v>79262</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>312</v>
+        <v>6305</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>choline</t>
+          <t>fish_oil</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>0.74</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.45</v>
+        <v>0.49</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>361.92</v>
+        <v>4.78</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>93.5</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.160920736648293</v>
+        <v>0.05582483881549636</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>79262</v>
+        <v>508253</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>6305</v>
+        <v>62658</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>fish_oil</t>
+          <t>folic_acid</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>0.74</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.49</v>
+        <v>0.66</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.11</v>
+        <v>0.83</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.11</v>
+        <v>0.45</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>4.78</v>
+        <v>1.23</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>87.40000000000001</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.05582483881549636</v>
+        <v>2.258290397247039e-05</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>508253</v>
+        <v>987993</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>62658</v>
+        <v>45499</v>
       </c>
     </row>
     <row r="24">
